--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/specialty_data.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/specialty_data.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -370,6 +370,21 @@
           <t>n_appts</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_percents</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_percents_label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -378,7 +393,20 @@
         </is>
       </c>
       <c r="C2">
-        <v>1965</v>
+        <v>719</v>
+      </c>
+      <c r="D2">
+        <v>78.67</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>719(78.67%)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>78.67%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -388,13 +416,26 @@
         </is>
       </c>
       <c r="C3">
-        <v>1803</v>
+        <v>195</v>
+      </c>
+      <c r="D3">
+        <v>21.33</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>195(21.33%)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>21.33%</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Speech and Language Therapy Service</t>
+          <t>adult mental health service</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -403,7 +444,20 @@
         </is>
       </c>
       <c r="C4">
-        <v>211</v>
+        <v>192</v>
+      </c>
+      <c r="D4">
+        <v>49.74</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>192(49.74%)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>49.74%</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -414,26 +468,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C5">
-        <v>1030</v>
+        <v>194</v>
+      </c>
+      <c r="D5">
+        <v>50.26</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>194(50.26%)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50.26%</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>adult mental health service</t>
+          <t>allergy service</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C6">
-        <v>1030</v>
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>48.28</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>14(48.28%)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>48.28%</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -444,26 +524,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C7">
-        <v>77</v>
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>51.72</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15(51.72%)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>51.72%</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>allergy service</t>
+          <t>anaesthetic service</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C8">
-        <v>83</v>
+        <v>375</v>
+      </c>
+      <c r="D8">
+        <v>50.07</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>375(50.07%)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>50.07%</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -474,26 +580,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C9">
-        <v>480</v>
+        <v>374</v>
+      </c>
+      <c r="D9">
+        <v>49.93</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>374(49.93%)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49.93%</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>anaesthetic service</t>
+          <t>anticoagulant service</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C10">
-        <v>478</v>
+        <v>298</v>
+      </c>
+      <c r="D10">
+        <v>49.92</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>298(49.92%)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>49.92%</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -504,17 +636,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C11">
-        <v>2976</v>
+        <v>299</v>
+      </c>
+      <c r="D11">
+        <v>50.08</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>299(50.08%)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50.08%</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>anticoagulant service</t>
+          <t>audio vestibular medicine service</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -523,22 +668,48 @@
         </is>
       </c>
       <c r="C12">
-        <v>2957</v>
+        <v>248</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>248(100%)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>audio vestibular medicine service</t>
+          <t>audiology service</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C13">
-        <v>569</v>
+        <v>787</v>
+      </c>
+      <c r="D13">
+        <v>50.03</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>787(50.03%)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50.03%</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -549,26 +720,52 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C14">
-        <v>1883</v>
+        <v>786</v>
+      </c>
+      <c r="D14">
+        <v>49.97</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>786(49.97%)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>49.97%</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>audiology service</t>
+          <t>blood and marrow transplantation service</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C15">
-        <v>1885</v>
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>50</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -579,32 +776,58 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
+      <c r="D16">
+        <v>50</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>blood and marrow transplantation service</t>
+          <t>breast surgery service</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>523</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>523(100%)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>breast surgery service</t>
+          <t>burns care service</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -613,7 +836,20 @@
         </is>
       </c>
       <c r="C18">
-        <v>848</v>
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>50</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6(50%)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -624,26 +860,52 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C19">
-        <v>48</v>
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>50</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6(50%)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>burns care service</t>
+          <t>cardiac rehabilitation service</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C20">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>50</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10(50%)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -654,26 +916,52 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C21">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>50</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10(50%)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cardiac rehabilitation service</t>
+          <t>cardiac surgery service</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C22">
-        <v>104</v>
+        <v>35</v>
+      </c>
+      <c r="D22">
+        <v>50</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>35(50%)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -684,26 +972,52 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C23">
-        <v>61</v>
+        <v>35</v>
+      </c>
+      <c r="D23">
+        <v>50</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>35(50%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cardiac surgery service</t>
+          <t>cardiology service</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C24">
-        <v>61</v>
+        <v>2015</v>
+      </c>
+      <c r="D24">
+        <v>49.94</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2,015(49.94%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>49.94%</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -714,26 +1028,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C25">
-        <v>4309</v>
+        <v>2020</v>
+      </c>
+      <c r="D25">
+        <v>50.06</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2,020(50.06%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>50.06%</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cardiology service</t>
+          <t>cardiothoracic surgery service</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C26">
-        <v>4300</v>
+        <v>33</v>
+      </c>
+      <c r="D26">
+        <v>50</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>33(50%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -744,26 +1084,52 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C27">
-        <v>53</v>
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>50</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>33(50%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cardiothoracic surgery service</t>
+          <t>cardiothoracic transplantation service</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C28">
-        <v>53</v>
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>50</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -774,26 +1140,52 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C29">
-        <v>56</v>
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>50</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cardiothoracic transplantation service</t>
+          <t>chemical pathology service</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C30">
-        <v>56</v>
+        <v>37</v>
+      </c>
+      <c r="D30">
+        <v>51.39</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>37(51.39%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>51.39%</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -804,26 +1196,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C31">
-        <v>101</v>
+        <v>35</v>
+      </c>
+      <c r="D31">
+        <v>48.61</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>35(48.61%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>48.61%</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>chemical pathology service</t>
+          <t>child and adolescent psychiatry service</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C32">
-        <v>93</v>
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>50</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -834,26 +1252,52 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>50</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>child and adolescent psychiatry service</t>
+          <t>clinical genetics service</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>50</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10(50%)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -864,26 +1308,52 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C35">
         <v>10</v>
       </c>
+      <c r="D35">
+        <v>50</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10(50%)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>clinical genetics service</t>
+          <t>clinical haematology service</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>477</v>
+      </c>
+      <c r="D36">
+        <v>50.05</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>477(50.05%)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50.05%</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -894,26 +1364,52 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C37">
-        <v>1600</v>
+        <v>476</v>
+      </c>
+      <c r="D37">
+        <v>49.95</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>476(49.95%)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>49.95%</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>clinical haematology service</t>
+          <t>clinical immunology and allergy service</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C38">
-        <v>1587</v>
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>50</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20(50%)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -924,26 +1420,52 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C39">
-        <v>47</v>
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>50</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20(50%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>clinical immunology and allergy service</t>
+          <t>clinical immunology service</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C40">
-        <v>44</v>
+        <v>12</v>
+      </c>
+      <c r="D40">
+        <v>48</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>12(48%)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -954,26 +1476,52 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C41">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="D41">
+        <v>52</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>13(52%)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>clinical immunology service</t>
+          <t>clinical microbiology service</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C42">
-        <v>37</v>
+        <v>7</v>
+      </c>
+      <c r="D42">
+        <v>50</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7(50%)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -984,17 +1532,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D43">
+        <v>50</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>7(50%)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>clinical microbiology service</t>
+          <t>clinical neurophysiology service</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1003,13 +1564,26 @@
         </is>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>225</v>
+      </c>
+      <c r="D44">
+        <v>100</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>225(100%)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>clinical neurophysiology service</t>
+          <t>clinical oncology service</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1018,13 +1592,26 @@
         </is>
       </c>
       <c r="C45">
-        <v>255</v>
+        <v>133</v>
+      </c>
+      <c r="D45">
+        <v>50.19</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>133(50.19%)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>50.19%</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>clinical neurophysiology service</t>
+          <t>clinical oncology service</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1033,13 +1620,26 @@
         </is>
       </c>
       <c r="C46">
-        <v>260</v>
+        <v>132</v>
+      </c>
+      <c r="D46">
+        <v>49.81</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>132(49.81%)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>49.81%</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>clinical oncology service</t>
+          <t>clinical pharmacology service</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1048,13 +1648,26 @@
         </is>
       </c>
       <c r="C47">
-        <v>586</v>
+        <v>7</v>
+      </c>
+      <c r="D47">
+        <v>50</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>7(50%)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>clinical oncology service</t>
+          <t>clinical pharmacology service</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1063,13 +1676,26 @@
         </is>
       </c>
       <c r="C48">
-        <v>567</v>
+        <v>7</v>
+      </c>
+      <c r="D48">
+        <v>50</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>7(50%)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>clinical pharmacology service</t>
+          <t>clinical physiology service</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1078,13 +1704,26 @@
         </is>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>502</v>
+      </c>
+      <c r="D49">
+        <v>49.95</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>502(49.95%)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>49.95%</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>clinical pharmacology service</t>
+          <t>clinical physiology service</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1093,13 +1732,26 @@
         </is>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>503</v>
+      </c>
+      <c r="D50">
+        <v>50.05</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>503(50.05%)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>50.05%</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>clinical physiology service</t>
+          <t>clinical psychology service</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1108,13 +1760,26 @@
         </is>
       </c>
       <c r="C51">
-        <v>748</v>
+        <v>19</v>
+      </c>
+      <c r="D51">
+        <v>50</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19(50%)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>clinical physiology service</t>
+          <t>clinical psychology service</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1123,13 +1788,26 @@
         </is>
       </c>
       <c r="C52">
-        <v>756</v>
+        <v>19</v>
+      </c>
+      <c r="D52">
+        <v>50</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19(50%)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>clinical psychology service</t>
+          <t>colorectal surgery service</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1138,13 +1816,26 @@
         </is>
       </c>
       <c r="C53">
-        <v>97</v>
+        <v>545</v>
+      </c>
+      <c r="D53">
+        <v>49.77</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>545(49.77%)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>49.77%</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>clinical psychology service</t>
+          <t>colorectal surgery service</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1153,13 +1844,26 @@
         </is>
       </c>
       <c r="C54">
-        <v>97</v>
+        <v>550</v>
+      </c>
+      <c r="D54">
+        <v>50.23</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>550(50.23%)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>50.23%</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>colorectal surgery service</t>
+          <t>complex specialised rehabilitation service</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1168,13 +1872,26 @@
         </is>
       </c>
       <c r="C55">
-        <v>827</v>
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>60</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3(60%)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>colorectal surgery service</t>
+          <t>complex specialised rehabilitation service</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1183,13 +1900,26 @@
         </is>
       </c>
       <c r="C56">
-        <v>831</v>
+        <v>2</v>
+      </c>
+      <c r="D56">
+        <v>40</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2(40%)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>complex specialised rehabilitation service</t>
+          <t>congenital heart disease service</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1198,13 +1928,26 @@
         </is>
       </c>
       <c r="C57">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>50</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2(50%)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>complex specialised rehabilitation service</t>
+          <t>congenital heart disease service</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1213,13 +1956,26 @@
         </is>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>50</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2(50%)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>congenital heart disease service</t>
+          <t>dental medicine service</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1228,13 +1984,26 @@
         </is>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="D59">
+        <v>49.57</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>58(49.57%)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>49.57%</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>congenital heart disease service</t>
+          <t>dental medicine service</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1243,13 +2012,26 @@
         </is>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>59</v>
+      </c>
+      <c r="D60">
+        <v>50.43</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>59(50.43%)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>50.43%</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dental medicine service</t>
+          <t>dermatology service</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1258,13 +2040,26 @@
         </is>
       </c>
       <c r="C61">
-        <v>130</v>
+        <v>1118</v>
+      </c>
+      <c r="D61">
+        <v>50.07</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1,118(50.07%)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>50.07%</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dental medicine service</t>
+          <t>dermatology service</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1273,13 +2068,26 @@
         </is>
       </c>
       <c r="C62">
-        <v>131</v>
+        <v>1115</v>
+      </c>
+      <c r="D62">
+        <v>49.93</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1,115(49.93%)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>49.93%</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dermatology service</t>
+          <t>diabetes service</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1288,13 +2096,26 @@
         </is>
       </c>
       <c r="C63">
-        <v>2835</v>
+        <v>268</v>
+      </c>
+      <c r="D63">
+        <v>50.28</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>268(50.28%)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.28%</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dermatology service</t>
+          <t>diabetes service</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1303,13 +2124,26 @@
         </is>
       </c>
       <c r="C64">
-        <v>2845</v>
+        <v>265</v>
+      </c>
+      <c r="D64">
+        <v>49.72</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>265(49.72%)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>49.72%</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>diabetes service</t>
+          <t>diagnostic imaging service</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1318,13 +2152,26 @@
         </is>
       </c>
       <c r="C65">
-        <v>929</v>
+        <v>2933</v>
+      </c>
+      <c r="D65">
+        <v>49.66</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2,933(49.66%)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>49.66%</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>diabetes service</t>
+          <t>diagnostic imaging service</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1333,13 +2180,26 @@
         </is>
       </c>
       <c r="C66">
-        <v>919</v>
+        <v>2973</v>
+      </c>
+      <c r="D66">
+        <v>50.34</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2,973(50.34%)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>50.34%</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>diagnostic imaging service</t>
+          <t>dietetics service</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1348,13 +2208,26 @@
         </is>
       </c>
       <c r="C67">
-        <v>5698</v>
+        <v>229</v>
+      </c>
+      <c r="D67">
+        <v>50.33</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>229(50.33%)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>50.33%</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>diagnostic imaging service</t>
+          <t>dietetics service</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1363,13 +2236,26 @@
         </is>
       </c>
       <c r="C68">
-        <v>5771</v>
+        <v>226</v>
+      </c>
+      <c r="D68">
+        <v>49.67</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>226(49.67%)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>49.67%</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dietetics service</t>
+          <t>ear nose and throat service</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1378,13 +2264,26 @@
         </is>
       </c>
       <c r="C69">
-        <v>622</v>
+        <v>1182</v>
+      </c>
+      <c r="D69">
+        <v>49.68</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1,182(49.68%)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>49.68%</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dietetics service</t>
+          <t>ear nose and throat service</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1393,13 +2292,26 @@
         </is>
       </c>
       <c r="C70">
-        <v>596</v>
+        <v>1197</v>
+      </c>
+      <c r="D70">
+        <v>50.32</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1,197(50.32%)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>50.32%</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ear nose and throat service</t>
+          <t>elderly medicine service</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1408,13 +2320,26 @@
         </is>
       </c>
       <c r="C71">
-        <v>2449</v>
+        <v>1345</v>
+      </c>
+      <c r="D71">
+        <v>49.47</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1,345(49.47%)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>49.47%</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ear nose and throat service</t>
+          <t>elderly medicine service</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1423,13 +2348,26 @@
         </is>
       </c>
       <c r="C72">
-        <v>2505</v>
+        <v>1374</v>
+      </c>
+      <c r="D72">
+        <v>50.53</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1,374(50.53%)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>50.53%</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>elderly medicine service</t>
+          <t>emergency medicine service</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1438,13 +2376,26 @@
         </is>
       </c>
       <c r="C73">
-        <v>3208</v>
+        <v>268</v>
+      </c>
+      <c r="D73">
+        <v>50</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>268(50%)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>elderly medicine service</t>
+          <t>emergency medicine service</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1453,13 +2404,26 @@
         </is>
       </c>
       <c r="C74">
-        <v>3317</v>
+        <v>268</v>
+      </c>
+      <c r="D74">
+        <v>50</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>268(50%)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>emergency medicine service</t>
+          <t>endocrinology service</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1468,13 +2432,26 @@
         </is>
       </c>
       <c r="C75">
-        <v>378</v>
+        <v>269</v>
+      </c>
+      <c r="D75">
+        <v>49.63</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>269(49.63%)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>49.63%</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>emergency medicine service</t>
+          <t>endocrinology service</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1483,13 +2460,26 @@
         </is>
       </c>
       <c r="C76">
-        <v>377</v>
+        <v>273</v>
+      </c>
+      <c r="D76">
+        <v>50.37</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>273(50.37%)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>50.37%</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>endocrinology service</t>
+          <t>gastroenterology service</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1498,13 +2488,26 @@
         </is>
       </c>
       <c r="C77">
-        <v>586</v>
+        <v>949</v>
+      </c>
+      <c r="D77">
+        <v>49.79</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>949(49.79%)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>49.79%</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>endocrinology service</t>
+          <t>gastroenterology service</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1513,13 +2516,26 @@
         </is>
       </c>
       <c r="C78">
-        <v>592</v>
+        <v>957</v>
+      </c>
+      <c r="D78">
+        <v>50.21</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>957(50.21%)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>50.21%</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>gastroenterology service</t>
+          <t>general internal medicine service</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1528,13 +2544,26 @@
         </is>
       </c>
       <c r="C79">
-        <v>1813</v>
+        <v>1126</v>
+      </c>
+      <c r="D79">
+        <v>49.67</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1,126(49.67%)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>49.67%</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>gastroenterology service</t>
+          <t>general internal medicine service</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1543,13 +2572,26 @@
         </is>
       </c>
       <c r="C80">
-        <v>1840</v>
+        <v>1141</v>
+      </c>
+      <c r="D80">
+        <v>50.33</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1,141(50.33%)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>50.33%</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>general internal medicine service</t>
+          <t>general surgery service</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1558,13 +2600,26 @@
         </is>
       </c>
       <c r="C81">
-        <v>3118</v>
+        <v>1062</v>
+      </c>
+      <c r="D81">
+        <v>50</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1,062(50%)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>general internal medicine service</t>
+          <t>general surgery service</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1573,13 +2628,26 @@
         </is>
       </c>
       <c r="C82">
-        <v>3137</v>
+        <v>1062</v>
+      </c>
+      <c r="D82">
+        <v>50</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1,062(50%)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>general surgery service</t>
+          <t>genitourinary medicine service</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1588,13 +2656,26 @@
         </is>
       </c>
       <c r="C83">
-        <v>1923</v>
+        <v>6</v>
+      </c>
+      <c r="D83">
+        <v>54.55</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>6(54.55%)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>54.55%</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>general surgery service</t>
+          <t>genitourinary medicine service</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1603,13 +2684,26 @@
         </is>
       </c>
       <c r="C84">
-        <v>1920</v>
+        <v>5</v>
+      </c>
+      <c r="D84">
+        <v>45.45</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>5(45.45%)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>45.45%</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>genitourinary medicine service</t>
+          <t>gynaecological oncology service</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1618,13 +2712,26 @@
         </is>
       </c>
       <c r="C85">
-        <v>11</v>
+        <v>115</v>
+      </c>
+      <c r="D85">
+        <v>49.57</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>115(49.57%)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>49.57%</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>genitourinary medicine service</t>
+          <t>gynaecological oncology service</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1633,13 +2740,26 @@
         </is>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>117</v>
+      </c>
+      <c r="D86">
+        <v>50.43</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>117(50.43%)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>50.43%</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gynaecological oncology service</t>
+          <t>gynaecology service</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1648,13 +2768,26 @@
         </is>
       </c>
       <c r="C87">
-        <v>199</v>
+        <v>904</v>
+      </c>
+      <c r="D87">
+        <v>50</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>904(50%)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>gynaecological oncology service</t>
+          <t>gynaecology service</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1663,118 +2796,222 @@
         </is>
       </c>
       <c r="C88">
-        <v>203</v>
+        <v>904</v>
+      </c>
+      <c r="D88">
+        <v>50</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>904(50%)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gynaecology service</t>
+          <t>haemophilia service</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C89">
-        <v>2016</v>
+        <v>7</v>
+      </c>
+      <c r="D89">
+        <v>100</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>7(100%)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gynaecology service</t>
+          <t>hepatobiliary and pancreatic surgery service</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C90">
-        <v>2008</v>
+        <v>31</v>
+      </c>
+      <c r="D90">
+        <v>50</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>31(50%)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>haemophilia service</t>
+          <t>hepatobiliary and pancreatic surgery service</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C91">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="D91">
+        <v>50</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>31(50%)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>haemophilia service</t>
+          <t>hepatology service</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C92">
-        <v>16</v>
+        <v>70</v>
+      </c>
+      <c r="D92">
+        <v>49.65</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>70(49.65%)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>49.65%</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>hepatobiliary and pancreatic surgery service</t>
+          <t>hepatology service</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C93">
-        <v>64</v>
+        <v>71</v>
+      </c>
+      <c r="D93">
+        <v>50.35</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>71(50.35%)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>50.35%</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>hepatobiliary and pancreatic surgery service</t>
+          <t>infectious diseases service</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C94">
-        <v>64</v>
+        <v>26</v>
+      </c>
+      <c r="D94">
+        <v>50</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>26(50%)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>hepatology service</t>
+          <t>infectious diseases service</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C95">
-        <v>144</v>
+        <v>26</v>
+      </c>
+      <c r="D95">
+        <v>50</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>26(50%)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>hepatology service</t>
+          <t>intensive care medicine service</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1783,13 +3020,26 @@
         </is>
       </c>
       <c r="C96">
-        <v>145</v>
+        <v>10</v>
+      </c>
+      <c r="D96">
+        <v>100</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>10(100%)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>infectious diseases service</t>
+          <t>intermediate care service</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1798,13 +3048,26 @@
         </is>
       </c>
       <c r="C97">
-        <v>58</v>
+        <v>168</v>
+      </c>
+      <c r="D97">
+        <v>55.26</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>168(55.26%)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>55.26%</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>infectious diseases service</t>
+          <t>intermediate care service</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1813,118 +3076,222 @@
         </is>
       </c>
       <c r="C98">
-        <v>58</v>
+        <v>136</v>
+      </c>
+      <c r="D98">
+        <v>44.74</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>136(44.74%)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>44.74%</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>intensive care medicine service</t>
+          <t>interventional radiology service</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C99">
-        <v>12</v>
+        <v>172</v>
+      </c>
+      <c r="D99">
+        <v>50.15</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>172(50.15%)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>50.15%</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>intermediate care service</t>
+          <t>interventional radiology service</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C100">
-        <v>2238</v>
+        <v>171</v>
+      </c>
+      <c r="D100">
+        <v>49.85</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>171(49.85%)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>49.85%</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>intermediate care service</t>
+          <t>learning disability service</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C101">
-        <v>1791</v>
+        <v>41</v>
+      </c>
+      <c r="D101">
+        <v>50</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>41(50%)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>interventional radiology service</t>
+          <t>learning disability service</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C102">
-        <v>304</v>
+        <v>41</v>
+      </c>
+      <c r="D102">
+        <v>50</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>41(50%)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>interventional radiology service</t>
+          <t>liaison psychiatry service</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C103">
-        <v>185</v>
+        <v>28</v>
+      </c>
+      <c r="D103">
+        <v>46.67</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>28(46.67%)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>46.67%</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>learning disability service</t>
+          <t>liaison psychiatry service</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C104">
-        <v>334</v>
+        <v>32</v>
+      </c>
+      <c r="D104">
+        <v>53.33</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>32(53.33%)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>53.33%</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>learning disability service</t>
+          <t>local specialist rehabilitation service</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C105">
-        <v>338</v>
+        <v>2</v>
+      </c>
+      <c r="D105">
+        <v>100</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2(100%)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>liaison psychiatry service</t>
+          <t>maxillofacial surgery service</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -1933,13 +3300,26 @@
         </is>
       </c>
       <c r="C106">
-        <v>88</v>
+        <v>258</v>
+      </c>
+      <c r="D106">
+        <v>50</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>258(50%)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>liaison psychiatry service</t>
+          <t>maxillofacial surgery service</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -1948,13 +3328,26 @@
         </is>
       </c>
       <c r="C107">
-        <v>94</v>
+        <v>258</v>
+      </c>
+      <c r="D107">
+        <v>50</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>258(50%)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>maxillofacial surgery service</t>
+          <t>medical oncology service</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -1963,13 +3356,26 @@
         </is>
       </c>
       <c r="C108">
-        <v>536</v>
+        <v>73</v>
+      </c>
+      <c r="D108">
+        <v>50</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>73(50%)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>maxillofacial surgery service</t>
+          <t>medical oncology service</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -1978,13 +3384,26 @@
         </is>
       </c>
       <c r="C109">
-        <v>539</v>
+        <v>73</v>
+      </c>
+      <c r="D109">
+        <v>50</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>73(50%)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>medical oncology service</t>
+          <t>medical ophthalmology service</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -1993,13 +3412,26 @@
         </is>
       </c>
       <c r="C110">
-        <v>298</v>
+        <v>57</v>
+      </c>
+      <c r="D110">
+        <v>49.57</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>57(49.57%)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>49.57%</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>medical oncology service</t>
+          <t>medical ophthalmology service</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2008,13 +3440,26 @@
         </is>
       </c>
       <c r="C111">
-        <v>388</v>
+        <v>58</v>
+      </c>
+      <c r="D111">
+        <v>50.43</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>58(50.43%)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>50.43%</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>medical ophthalmology service</t>
+          <t>medical psychotherapy service</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2023,13 +3468,26 @@
         </is>
       </c>
       <c r="C112">
-        <v>125</v>
+        <v>3</v>
+      </c>
+      <c r="D112">
+        <v>50</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>medical ophthalmology service</t>
+          <t>medical psychotherapy service</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2038,13 +3496,26 @@
         </is>
       </c>
       <c r="C113">
-        <v>128</v>
+        <v>3</v>
+      </c>
+      <c r="D113">
+        <v>50</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>medical psychotherapy service</t>
+          <t>neurology service</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2053,13 +3524,26 @@
         </is>
       </c>
       <c r="C114">
-        <v>6</v>
+        <v>762</v>
+      </c>
+      <c r="D114">
+        <v>49.9</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>762(49.9%)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>49.9%</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>medical psychotherapy service</t>
+          <t>neurology service</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2068,13 +3552,26 @@
         </is>
       </c>
       <c r="C115">
-        <v>6</v>
+        <v>765</v>
+      </c>
+      <c r="D115">
+        <v>50.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>765(50.1%)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>50.1%</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>neurology service</t>
+          <t>neurosurgical service</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2083,13 +3580,26 @@
         </is>
       </c>
       <c r="C116">
-        <v>1700</v>
+        <v>301</v>
+      </c>
+      <c r="D116">
+        <v>50</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>301(50%)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>neurology service</t>
+          <t>neurosurgical service</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2098,13 +3608,26 @@
         </is>
       </c>
       <c r="C117">
-        <v>1718</v>
+        <v>301</v>
+      </c>
+      <c r="D117">
+        <v>50</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>301(50%)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>neurosurgical service</t>
+          <t>nuclear medicine service</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2113,13 +3636,26 @@
         </is>
       </c>
       <c r="C118">
-        <v>661</v>
+        <v>30</v>
+      </c>
+      <c r="D118">
+        <v>50.85</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>30(50.85%)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>50.85%</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>neurosurgical service</t>
+          <t>nuclear medicine service</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2128,13 +3664,26 @@
         </is>
       </c>
       <c r="C119">
-        <v>656</v>
+        <v>29</v>
+      </c>
+      <c r="D119">
+        <v>49.15</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>29(49.15%)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>49.15%</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>nuclear medicine service</t>
+          <t>obstetrics service</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2143,13 +3692,26 @@
         </is>
       </c>
       <c r="C120">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="D120">
+        <v>44.44</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>4(44.44%)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>44.44%</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>nuclear medicine service</t>
+          <t>obstetrics service</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2158,13 +3720,26 @@
         </is>
       </c>
       <c r="C121">
-        <v>54</v>
+        <v>5</v>
+      </c>
+      <c r="D121">
+        <v>55.56</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>5(55.56%)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>55.56%</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>obstetrics service</t>
+          <t>occupational therapy service</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2173,13 +3748,26 @@
         </is>
       </c>
       <c r="C122">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="D122">
+        <v>49.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>616(49.8%)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>49.8%</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>obstetrics service</t>
+          <t>occupational therapy service</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2188,13 +3776,26 @@
         </is>
       </c>
       <c r="C123">
-        <v>6</v>
+        <v>621</v>
+      </c>
+      <c r="D123">
+        <v>50.2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>621(50.2%)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>50.2%</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>occupational therapy service</t>
+          <t>old age psychiatry service</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2203,13 +3804,26 @@
         </is>
       </c>
       <c r="C124">
-        <v>2747</v>
+        <v>464</v>
+      </c>
+      <c r="D124">
+        <v>49.52</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>464(49.52%)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>49.52%</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>occupational therapy service</t>
+          <t>old age psychiatry service</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2218,13 +3832,26 @@
         </is>
       </c>
       <c r="C125">
-        <v>2770</v>
+        <v>473</v>
+      </c>
+      <c r="D125">
+        <v>50.48</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>473(50.48%)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>50.48%</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>old age psychiatry service</t>
+          <t>ophthalmology service</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2233,13 +3860,26 @@
         </is>
       </c>
       <c r="C126">
-        <v>1422</v>
+        <v>3308</v>
+      </c>
+      <c r="D126">
+        <v>49.83</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>3,308(49.83%)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>49.83%</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>old age psychiatry service</t>
+          <t>ophthalmology service</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2248,13 +3888,26 @@
         </is>
       </c>
       <c r="C127">
-        <v>1439</v>
+        <v>3331</v>
+      </c>
+      <c r="D127">
+        <v>50.17</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>3,331(50.17%)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>50.17%</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ophthalmology service</t>
+          <t>optometry service</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2263,13 +3916,26 @@
         </is>
       </c>
       <c r="C128">
-        <v>11730</v>
+        <v>37</v>
+      </c>
+      <c r="D128">
+        <v>48.05</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>37(48.05%)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>48.05%</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ophthalmology service</t>
+          <t>optometry service</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2278,13 +3944,26 @@
         </is>
       </c>
       <c r="C129">
-        <v>11738</v>
+        <v>40</v>
+      </c>
+      <c r="D129">
+        <v>51.95</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>40(51.95%)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>51.95%</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>optometry service</t>
+          <t>oral surgery service</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2293,13 +3972,26 @@
         </is>
       </c>
       <c r="C130">
-        <v>54</v>
+        <v>350</v>
+      </c>
+      <c r="D130">
+        <v>49.86</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>350(49.86%)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>49.86%</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>optometry service</t>
+          <t>oral surgery service</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2308,13 +4000,26 @@
         </is>
       </c>
       <c r="C131">
-        <v>57</v>
+        <v>352</v>
+      </c>
+      <c r="D131">
+        <v>50.14</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>352(50.14%)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>50.14%</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>oral surgery service</t>
+          <t>orthodontic service</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2323,13 +4028,26 @@
         </is>
       </c>
       <c r="C132">
-        <v>675</v>
+        <v>3</v>
+      </c>
+      <c r="D132">
+        <v>50</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>oral surgery service</t>
+          <t>orthodontic service</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2338,13 +4056,26 @@
         </is>
       </c>
       <c r="C133">
-        <v>676</v>
+        <v>3</v>
+      </c>
+      <c r="D133">
+        <v>50</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>orthodontic service</t>
+          <t>orthoptics service</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2353,13 +4084,26 @@
         </is>
       </c>
       <c r="C134">
-        <v>3</v>
+        <v>178</v>
+      </c>
+      <c r="D134">
+        <v>50</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>178(50%)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>orthodontic service</t>
+          <t>orthoptics service</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2368,13 +4112,26 @@
         </is>
       </c>
       <c r="C135">
-        <v>3</v>
+        <v>178</v>
+      </c>
+      <c r="D135">
+        <v>50</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>178(50%)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>orthoptics service</t>
+          <t>orthotics service</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2383,13 +4140,26 @@
         </is>
       </c>
       <c r="C136">
-        <v>328</v>
+        <v>252</v>
+      </c>
+      <c r="D136">
+        <v>49.7</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>252(49.7%)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>49.7%</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>orthoptics service</t>
+          <t>orthotics service</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2398,13 +4168,26 @@
         </is>
       </c>
       <c r="C137">
-        <v>326</v>
+        <v>255</v>
+      </c>
+      <c r="D137">
+        <v>50.3</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>255(50.3%)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>orthotics service</t>
+          <t>paediatric ear nose and throat service</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2413,13 +4196,26 @@
         </is>
       </c>
       <c r="C138">
-        <v>481</v>
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>50</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>orthotics service</t>
+          <t>paediatric ear nose and throat service</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2428,13 +4224,26 @@
         </is>
       </c>
       <c r="C139">
-        <v>485</v>
+        <v>1</v>
+      </c>
+      <c r="D139">
+        <v>50</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>paediatric ear nose and throat service</t>
+          <t>paediatric ophthalmology service</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2443,13 +4252,26 @@
         </is>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D140">
+        <v>50</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>7(50%)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>paediatric ear nose and throat service</t>
+          <t>paediatric ophthalmology service</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2458,13 +4280,26 @@
         </is>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D141">
+        <v>50</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>7(50%)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>paediatric ophthalmology service</t>
+          <t>paediatric service</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2473,13 +4308,26 @@
         </is>
       </c>
       <c r="C142">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="D142">
+        <v>50</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2(50%)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>paediatric ophthalmology service</t>
+          <t>paediatric service</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2488,13 +4336,26 @@
         </is>
       </c>
       <c r="C143">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="D143">
+        <v>50</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2(50%)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>paediatric service</t>
+          <t>paediatric trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2503,13 +4364,26 @@
         </is>
       </c>
       <c r="C144">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="D144">
+        <v>50</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>15(50%)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>paediatric service</t>
+          <t>paediatric trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2518,13 +4392,26 @@
         </is>
       </c>
       <c r="C145">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="D145">
+        <v>50</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>15(50%)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>paediatric trauma and orthopaedic service</t>
+          <t>pain management service</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2533,13 +4420,26 @@
         </is>
       </c>
       <c r="C146">
-        <v>18</v>
+        <v>473</v>
+      </c>
+      <c r="D146">
+        <v>49.58</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>473(49.58%)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>49.58%</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>paediatric trauma and orthopaedic service</t>
+          <t>pain management service</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2548,13 +4448,26 @@
         </is>
       </c>
       <c r="C147">
-        <v>18</v>
+        <v>481</v>
+      </c>
+      <c r="D147">
+        <v>50.42</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>481(50.42%)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>50.42%</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>pain management service</t>
+          <t>palliative medicine service</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2563,13 +4476,26 @@
         </is>
       </c>
       <c r="C148">
-        <v>1186</v>
+        <v>34</v>
+      </c>
+      <c r="D148">
+        <v>50.75</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>34(50.75%)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>50.75%</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>pain management service</t>
+          <t>palliative medicine service</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2578,13 +4504,26 @@
         </is>
       </c>
       <c r="C149">
-        <v>1208</v>
+        <v>33</v>
+      </c>
+      <c r="D149">
+        <v>49.25</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>33(49.25%)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>49.25%</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>palliative medicine service</t>
+          <t>physiotherapy service</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2593,13 +4532,26 @@
         </is>
       </c>
       <c r="C150">
-        <v>212</v>
+        <v>5351</v>
+      </c>
+      <c r="D150">
+        <v>49.66</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>5,351(49.66%)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>49.66%</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>palliative medicine service</t>
+          <t>physiotherapy service</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2608,13 +4560,26 @@
         </is>
       </c>
       <c r="C151">
-        <v>210</v>
+        <v>5425</v>
+      </c>
+      <c r="D151">
+        <v>50.34</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>5,425(50.34%)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>50.34%</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>physiotherapy service</t>
+          <t>plastic surgery service</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2623,13 +4588,26 @@
         </is>
       </c>
       <c r="C152">
-        <v>26485</v>
+        <v>357</v>
+      </c>
+      <c r="D152">
+        <v>49.86</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>357(49.86%)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>49.86%</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>physiotherapy service</t>
+          <t>plastic surgery service</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2638,13 +4616,26 @@
         </is>
       </c>
       <c r="C153">
-        <v>26819</v>
+        <v>359</v>
+      </c>
+      <c r="D153">
+        <v>50.14</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>359(50.14%)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>50.14%</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>plastic surgery service</t>
+          <t>podiatric surgery service</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2653,13 +4644,26 @@
         </is>
       </c>
       <c r="C154">
-        <v>1061</v>
+        <v>15</v>
+      </c>
+      <c r="D154">
+        <v>50</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>15(50%)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>plastic surgery service</t>
+          <t>podiatric surgery service</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2668,13 +4672,26 @@
         </is>
       </c>
       <c r="C155">
-        <v>1066</v>
+        <v>15</v>
+      </c>
+      <c r="D155">
+        <v>50</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>15(50%)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>podiatric surgery service</t>
+          <t>podiatry service</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2683,13 +4700,26 @@
         </is>
       </c>
       <c r="C156">
-        <v>44</v>
+        <v>372</v>
+      </c>
+      <c r="D156">
+        <v>50</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>372(50%)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>podiatric surgery service</t>
+          <t>podiatry service</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2698,13 +4728,26 @@
         </is>
       </c>
       <c r="C157">
-        <v>44</v>
+        <v>372</v>
+      </c>
+      <c r="D157">
+        <v>50</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>372(50%)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>podiatry service</t>
+          <t>prosthetics service</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2713,13 +4756,26 @@
         </is>
       </c>
       <c r="C158">
-        <v>1509</v>
+        <v>4</v>
+      </c>
+      <c r="D158">
+        <v>50</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>4(50%)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>podiatry service</t>
+          <t>prosthetics service</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2728,13 +4784,26 @@
         </is>
       </c>
       <c r="C159">
-        <v>1501</v>
+        <v>4</v>
+      </c>
+      <c r="D159">
+        <v>50</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>4(50%)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>prosthetics service</t>
+          <t>pulmonary rehabilitation service</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2745,11 +4814,24 @@
       <c r="C160">
         <v>6</v>
       </c>
+      <c r="D160">
+        <v>50</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>6(50%)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>prosthetics service</t>
+          <t>pulmonary rehabilitation service</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2760,11 +4842,24 @@
       <c r="C161">
         <v>6</v>
       </c>
+      <c r="D161">
+        <v>50</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>6(50%)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>pulmonary rehabilitation service</t>
+          <t>rehabilitation medicine service</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2773,13 +4868,26 @@
         </is>
       </c>
       <c r="C162">
-        <v>10</v>
+        <v>318</v>
+      </c>
+      <c r="D162">
+        <v>50.08</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>318(50.08%)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>50.08%</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>pulmonary rehabilitation service</t>
+          <t>rehabilitation medicine service</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2788,13 +4896,26 @@
         </is>
       </c>
       <c r="C163">
-        <v>10</v>
+        <v>317</v>
+      </c>
+      <c r="D163">
+        <v>49.92</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>317(49.92%)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>49.92%</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>rehabilitation medicine service</t>
+          <t>renal medicine service</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2803,13 +4924,26 @@
         </is>
       </c>
       <c r="C164">
-        <v>1378</v>
+        <v>259</v>
+      </c>
+      <c r="D164">
+        <v>49.43</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>259(49.43%)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>49.43%</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>rehabilitation medicine service</t>
+          <t>renal medicine service</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2818,13 +4952,26 @@
         </is>
       </c>
       <c r="C165">
-        <v>1397</v>
+        <v>265</v>
+      </c>
+      <c r="D165">
+        <v>50.57</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>265(50.57%)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>50.57%</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>renal medicine service</t>
+          <t>respiratory medicine service</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2833,13 +4980,26 @@
         </is>
       </c>
       <c r="C166">
-        <v>959</v>
+        <v>867</v>
+      </c>
+      <c r="D166">
+        <v>49.97</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>867(49.97%)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>49.97%</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>renal medicine service</t>
+          <t>respiratory medicine service</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2848,13 +5008,26 @@
         </is>
       </c>
       <c r="C167">
-        <v>955</v>
+        <v>868</v>
+      </c>
+      <c r="D167">
+        <v>50.03</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>868(50.03%)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>50.03%</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>respiratory medicine service</t>
+          <t>respiratory physiology service</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2863,13 +5036,26 @@
         </is>
       </c>
       <c r="C168">
-        <v>2504</v>
+        <v>125</v>
+      </c>
+      <c r="D168">
+        <v>50.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>125(50.4%)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>50.4%</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>respiratory medicine service</t>
+          <t>respiratory physiology service</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2878,13 +5064,26 @@
         </is>
       </c>
       <c r="C169">
-        <v>2529</v>
+        <v>123</v>
+      </c>
+      <c r="D169">
+        <v>49.6</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>123(49.6%)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>49.6%</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>respiratory physiology service</t>
+          <t>restorative dentistry service</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2893,13 +5092,26 @@
         </is>
       </c>
       <c r="C170">
-        <v>225</v>
+        <v>86</v>
+      </c>
+      <c r="D170">
+        <v>50</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>86(50%)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>respiratory physiology service</t>
+          <t>restorative dentistry service</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2908,13 +5120,26 @@
         </is>
       </c>
       <c r="C171">
-        <v>220</v>
+        <v>86</v>
+      </c>
+      <c r="D171">
+        <v>50</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>86(50%)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>restorative dentistry service</t>
+          <t>rheumatology service</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -2923,13 +5148,26 @@
         </is>
       </c>
       <c r="C172">
-        <v>331</v>
+        <v>2194</v>
+      </c>
+      <c r="D172">
+        <v>50.01</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2,194(50.01%)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>50.01%</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>restorative dentistry service</t>
+          <t>rheumatology service</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -2938,28 +5176,54 @@
         </is>
       </c>
       <c r="C173">
-        <v>336</v>
+        <v>2193</v>
+      </c>
+      <c r="D173">
+        <v>49.99</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2,193(49.99%)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>49.99%</t>
+        </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>rheumatology service</t>
+          <t>specialist rehabilitation service</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C174">
-        <v>5236</v>
+        <v>2</v>
+      </c>
+      <c r="D174">
+        <v>100</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2(100%)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>rheumatology service</t>
+          <t>speech and language therapy service</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -2968,13 +5232,26 @@
         </is>
       </c>
       <c r="C175">
-        <v>5218</v>
+        <v>88</v>
+      </c>
+      <c r="D175">
+        <v>100</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>88(100%)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>specialist rehabilitation service</t>
+          <t>spinal injuries service</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -2983,13 +5260,26 @@
         </is>
       </c>
       <c r="C176">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="D176">
+        <v>50</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>10(50%)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>specialist rehabilitation service</t>
+          <t>spinal injuries service</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -2998,253 +5288,474 @@
         </is>
       </c>
       <c r="C177">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="D177">
+        <v>50</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>10(50%)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>speech and language therapy service</t>
+          <t>spinal surgery service</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C178">
-        <v>215</v>
+        <v>175</v>
+      </c>
+      <c r="D178">
+        <v>50.58</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>175(50.58%)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>50.58%</t>
+        </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>spinal injuries service</t>
+          <t>spinal surgery service</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C179">
-        <v>34</v>
+        <v>171</v>
+      </c>
+      <c r="D179">
+        <v>49.42</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>171(49.42%)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>49.42%</t>
+        </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>spinal injuries service</t>
+          <t>sport and exercise medicine service</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C180">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>50</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>spinal surgery service</t>
+          <t>sport and exercise medicine service</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C181">
-        <v>401</v>
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>50</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1(50%)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>spinal surgery service</t>
+          <t>stroke medicine service</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C182">
-        <v>390</v>
+        <v>57</v>
+      </c>
+      <c r="D182">
+        <v>48.31</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>57(48.31%)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>48.31%</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>sport and exercise medicine service</t>
+          <t>stroke medicine service</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C183">
-        <v>4</v>
+        <v>61</v>
+      </c>
+      <c r="D183">
+        <v>51.69</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>61(51.69%)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>51.69%</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>sport and exercise medicine service</t>
+          <t>thoracic surgery service</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C184">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="D184">
+        <v>48.84</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>21(48.84%)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>48.84%</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>stroke medicine service</t>
+          <t>thoracic surgery service</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C185">
-        <v>75</v>
+        <v>22</v>
+      </c>
+      <c r="D185">
+        <v>51.16</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>22(51.16%)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>51.16%</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>stroke medicine service</t>
+          <t>transient ischaemic attack service</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C186">
-        <v>79</v>
+        <v>116</v>
+      </c>
+      <c r="D186">
+        <v>49.79</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>116(49.79%)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>49.79%</t>
+        </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>thoracic surgery service</t>
+          <t>transient ischaemic attack service</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C187">
-        <v>38</v>
+        <v>117</v>
+      </c>
+      <c r="D187">
+        <v>50.21</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>117(50.21%)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>50.21%</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>thoracic surgery service</t>
+          <t>transplant surgery service</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C188">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="D188">
+        <v>52.17</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>12(52.17%)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>52.17%</t>
+        </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>transient ischaemic attack service</t>
+          <t>transplant surgery service</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C189">
-        <v>141</v>
+        <v>11</v>
+      </c>
+      <c r="D189">
+        <v>47.83</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>11(47.83%)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>47.83%</t>
+        </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>transient ischaemic attack service</t>
+          <t>trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C190">
-        <v>142</v>
+        <v>16620</v>
+      </c>
+      <c r="D190">
+        <v>49.74</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>16,620(49.74%)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>49.74%</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>transplant surgery service</t>
+          <t>trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C191">
-        <v>41</v>
+        <v>16794</v>
+      </c>
+      <c r="D191">
+        <v>50.26</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>16,794(50.26%)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>50.26%</t>
+        </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>transplant surgery service</t>
+          <t>tropical medicine service</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C192">
-        <v>33</v>
+        <v>3</v>
+      </c>
+      <c r="D192">
+        <v>50</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>trauma and orthopaedic service</t>
+          <t>tropical medicine service</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C193">
-        <v>54293</v>
+        <v>3</v>
+      </c>
+      <c r="D193">
+        <v>50</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>3(50%)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>trauma and orthopaedic service</t>
+          <t>upper gastrointenstinal surgery service</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3253,13 +5764,26 @@
         </is>
       </c>
       <c r="C194">
-        <v>54893</v>
+        <v>90</v>
+      </c>
+      <c r="D194">
+        <v>100</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>90(100%)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>tropical medicine service</t>
+          <t>upper gastrointestinal surgery service</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3268,28 +5792,54 @@
         </is>
       </c>
       <c r="C195">
-        <v>3</v>
+        <v>89</v>
+      </c>
+      <c r="D195">
+        <v>100</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>89(100%)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>tropical medicine service</t>
+          <t>urology service</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C196">
-        <v>3</v>
+        <v>552</v>
+      </c>
+      <c r="D196">
+        <v>34.61</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>552(34.61%)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>34.61%</t>
+        </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>upper gastrointenstinal surgery service</t>
+          <t>urology service</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3298,13 +5848,26 @@
         </is>
       </c>
       <c r="C197">
-        <v>144</v>
+        <v>1043</v>
+      </c>
+      <c r="D197">
+        <v>65.39</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>1,043(65.39%)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>65.39%</t>
+        </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>upper gastrointestinal surgery service</t>
+          <t>vascular surgery service</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3313,67 +5876,48 @@
         </is>
       </c>
       <c r="C198">
-        <v>141</v>
+        <v>344</v>
+      </c>
+      <c r="D198">
+        <v>49.57</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>344(49.57%)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>49.57%</t>
+        </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>urology service</t>
+          <t>vascular surgery service</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C199">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>urology service</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SOURCE</t>
-        </is>
-      </c>
-      <c r="C200">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>vascular surgery service</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>OMOP</t>
-        </is>
-      </c>
-      <c r="C201">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>vascular surgery service</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>SOURCE</t>
-        </is>
-      </c>
-      <c r="C202">
-        <v>645</v>
+        <v>350</v>
+      </c>
+      <c r="D199">
+        <v>50.43</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>350(50.43%)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>50.43%</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/specialty_data.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/specialty_data.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -393,19 +393,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>719</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>78.67</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>719(78.67%)</t>
+          <t>18(8.45%)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78.67%</t>
+          <t>8.45%</t>
         </is>
       </c>
     </row>
@@ -419,16 +419,16 @@
         <v>195</v>
       </c>
       <c r="D3">
-        <v>21.33</v>
+        <v>91.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>195(21.33%)</t>
+          <t>195(91.55%)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.33%</t>
+          <t>91.55%</t>
         </is>
       </c>
     </row>
@@ -440,51 +440,51 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C4">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D4">
-        <v>49.74</v>
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>192(49.74%)</t>
+          <t>194(100%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.74%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>adult mental health service</t>
+          <t>allergy service</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C5">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>50.26</v>
+        <v>48.28</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>194(50.26%)</t>
+          <t>14(48.28%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.26%</t>
+          <t>48.28%</t>
         </is>
       </c>
     </row>
@@ -496,51 +496,51 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>48.28</v>
+        <v>51.72</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14(48.28%)</t>
+          <t>15(51.72%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.28%</t>
+          <t>51.72%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>allergy service</t>
+          <t>anaesthetic service</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>375</v>
       </c>
       <c r="D7">
-        <v>51.72</v>
+        <v>50.07</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15(51.72%)</t>
+          <t>375(50.07%)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.72%</t>
+          <t>50.07%</t>
         </is>
       </c>
     </row>
@@ -552,51 +552,51 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C8">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D8">
-        <v>50.07</v>
+        <v>49.93</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>375(50.07%)</t>
+          <t>374(49.93%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.07%</t>
+          <t>49.93%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anaesthetic service</t>
+          <t>anticoagulant service</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C9">
-        <v>374</v>
+        <v>298</v>
       </c>
       <c r="D9">
-        <v>49.93</v>
+        <v>49.92</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>374(49.93%)</t>
+          <t>298(49.92%)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.93%</t>
+          <t>49.92%</t>
         </is>
       </c>
     </row>
@@ -608,30 +608,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C10">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D10">
-        <v>49.92</v>
+        <v>50.08</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>298(49.92%)</t>
+          <t>299(50.08%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.92%</t>
+          <t>50.08%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>anticoagulant service</t>
+          <t>audio vestibular medicine service</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -640,47 +640,47 @@
         </is>
       </c>
       <c r="C11">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="D11">
-        <v>50.08</v>
+        <v>100</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>299(50.08%)</t>
+          <t>248(100%)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.08%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>audio vestibular medicine service</t>
+          <t>audiology service</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C12">
-        <v>248</v>
+        <v>1006</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>56.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>248(100%)</t>
+          <t>1,006(56.14%)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56.14%</t>
         </is>
       </c>
     </row>
@@ -692,51 +692,51 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C13">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D13">
-        <v>50.03</v>
+        <v>43.86</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>787(50.03%)</t>
+          <t>786(43.86%)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>50.03%</t>
+          <t>43.86%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>audiology service</t>
+          <t>blood and marrow transplantation service</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C14">
-        <v>786</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>49.97</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>786(49.97%)</t>
+          <t>1(50%)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>49.97%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C15">
@@ -771,35 +771,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>blood and marrow transplantation service</t>
+          <t>breast surgery service</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>523</v>
       </c>
       <c r="D16">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1(50%)</t>
+          <t>523(100%)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>breast surgery service</t>
+          <t>burns care service</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>523</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>523(100%)</t>
+          <t>6(50%)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C18">
@@ -855,23 +855,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>burns care service</t>
+          <t>cardiac rehabilitation service</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>50</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6(50%)</t>
+          <t>10(50%)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C20">
@@ -911,23 +911,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cardiac rehabilitation service</t>
+          <t>cardiac surgery service</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D21">
         <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10(50%)</t>
+          <t>35(50%)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C22">
@@ -967,28 +967,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cardiac surgery service</t>
+          <t>cardiology service</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C23">
-        <v>35</v>
+        <v>2015</v>
       </c>
       <c r="D23">
-        <v>50</v>
+        <v>49.94</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35(50%)</t>
+          <t>2,015(49.94%)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.94%</t>
         </is>
       </c>
     </row>
@@ -1000,51 +1000,51 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C24">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D24">
-        <v>49.94</v>
+        <v>50.06</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2,015(49.94%)</t>
+          <t>2,020(50.06%)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>49.94%</t>
+          <t>50.06%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cardiology service</t>
+          <t>cardiothoracic surgery service</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C25">
-        <v>2020</v>
+        <v>33</v>
       </c>
       <c r="D25">
-        <v>50.06</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2,020(50.06%)</t>
+          <t>33(50%)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>50.06%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C26">
@@ -1079,23 +1079,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cardiothoracic surgery service</t>
+          <t>cardiothoracic transplantation service</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C27">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D27">
         <v>50</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33(50%)</t>
+          <t>3(50%)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C28">
@@ -1135,28 +1135,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cardiothoracic transplantation service</t>
+          <t>chemical pathology service</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D29">
-        <v>50</v>
+        <v>51.39</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3(50%)</t>
+          <t>37(51.39%)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51.39%</t>
         </is>
       </c>
     </row>
@@ -1168,51 +1168,51 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C30">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D30">
-        <v>51.39</v>
+        <v>48.61</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37(51.39%)</t>
+          <t>35(48.61%)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>51.39%</t>
+          <t>48.61%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chemical pathology service</t>
+          <t>child and adolescent psychiatry service</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C31">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>48.61</v>
+        <v>50</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35(48.61%)</t>
+          <t>1(50%)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.61%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C32">
@@ -1247,23 +1247,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>child and adolescent psychiatry service</t>
+          <t>clinical genetics service</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>50</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1(50%)</t>
+          <t>10(50%)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C34">
@@ -1303,28 +1303,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>clinical genetics service</t>
+          <t>clinical haematology service</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>477</v>
       </c>
       <c r="D35">
-        <v>50</v>
+        <v>50.05</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10(50%)</t>
+          <t>477(50.05%)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.05%</t>
         </is>
       </c>
     </row>
@@ -1336,51 +1336,51 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C36">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D36">
-        <v>50.05</v>
+        <v>49.95</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>477(50.05%)</t>
+          <t>476(49.95%)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>50.05%</t>
+          <t>49.95%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>clinical haematology service</t>
+          <t>clinical immunology and allergy service</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C37">
-        <v>476</v>
+        <v>20</v>
       </c>
       <c r="D37">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>476(49.95%)</t>
+          <t>20(50%)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>49.95%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C38">
@@ -1415,28 +1415,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>clinical immunology and allergy service</t>
+          <t>clinical immunology service</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C39">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D39">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20(50%)</t>
+          <t>12(48%)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>48%</t>
         </is>
       </c>
     </row>
@@ -1448,51 +1448,51 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D40">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12(48%)</t>
+          <t>13(52%)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>52%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>clinical immunology service</t>
+          <t>clinical microbiology service</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D41">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13(52%)</t>
+          <t>7(50%)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C42">
@@ -1527,28 +1527,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>clinical microbiology service</t>
+          <t>clinical neurophysiology service</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>221</v>
       </c>
       <c r="D43">
-        <v>50</v>
+        <v>49.55</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7(50%)</t>
+          <t>221(49.55%)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.55%</t>
         </is>
       </c>
     </row>
@@ -1567,16 +1567,16 @@
         <v>225</v>
       </c>
       <c r="D44">
-        <v>100</v>
+        <v>50.45</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>225(100%)</t>
+          <t>225(50.45%)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50.45%</t>
         </is>
       </c>
     </row>
@@ -1700,51 +1700,51 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C49">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D49">
-        <v>49.95</v>
+        <v>100</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>502(49.95%)</t>
+          <t>503(100%)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>49.95%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>clinical physiology service</t>
+          <t>clinical psychology service</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C50">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D50">
-        <v>50.05</v>
+        <v>96.47</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>503(50.05%)</t>
+          <t>520(96.47%)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>50.05%</t>
+          <t>96.47%</t>
         </is>
       </c>
     </row>
@@ -1756,51 +1756,51 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C51">
         <v>19</v>
       </c>
       <c r="D51">
-        <v>50</v>
+        <v>3.53</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19(50%)</t>
+          <t>19(3.53%)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>clinical psychology service</t>
+          <t>colorectal surgery service</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C52">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="D52">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19(50%)</t>
+          <t>545(49.77%)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.77%</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1812,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C53">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D53">
-        <v>49.77</v>
+        <v>50.23</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>545(49.77%)</t>
+          <t>550(50.23%)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>49.77%</t>
+          <t>50.23%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>colorectal surgery service</t>
+          <t>complex specialised rehabilitation service</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1844,26 +1844,26 @@
         </is>
       </c>
       <c r="C54">
-        <v>550</v>
+        <v>2</v>
       </c>
       <c r="D54">
-        <v>50.23</v>
+        <v>100</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>550(50.23%)</t>
+          <t>2(100%)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>50.23%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>complex specialised rehabilitation service</t>
+          <t>congenital heart disease service</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1872,26 +1872,26 @@
         </is>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3(60%)</t>
+          <t>2(50%)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>complex specialised rehabilitation service</t>
+          <t>congenital heart disease service</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1903,23 +1903,23 @@
         <v>2</v>
       </c>
       <c r="D56">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2(40%)</t>
+          <t>2(50%)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>congenital heart disease service</t>
+          <t>dental medicine service</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1928,26 +1928,26 @@
         </is>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D57">
-        <v>50</v>
+        <v>49.57</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2(50%)</t>
+          <t>58(49.57%)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.57%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>congenital heart disease service</t>
+          <t>dental medicine service</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1956,26 +1956,26 @@
         </is>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D58">
-        <v>50</v>
+        <v>50.43</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2(50%)</t>
+          <t>59(50.43%)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.43%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dental medicine service</t>
+          <t>dermatology service</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1984,26 +1984,26 @@
         </is>
       </c>
       <c r="C59">
-        <v>58</v>
+        <v>1118</v>
       </c>
       <c r="D59">
-        <v>49.57</v>
+        <v>50.07</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58(49.57%)</t>
+          <t>1,118(50.07%)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>49.57%</t>
+          <t>50.07%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dental medicine service</t>
+          <t>dermatology service</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2012,26 +2012,26 @@
         </is>
       </c>
       <c r="C60">
-        <v>59</v>
+        <v>1115</v>
       </c>
       <c r="D60">
-        <v>50.43</v>
+        <v>49.93</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>59(50.43%)</t>
+          <t>1,115(49.93%)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>50.43%</t>
+          <t>49.93%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dermatology service</t>
+          <t>diabetes service</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2040,26 +2040,26 @@
         </is>
       </c>
       <c r="C61">
-        <v>1118</v>
+        <v>268</v>
       </c>
       <c r="D61">
-        <v>50.07</v>
+        <v>50.28</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1,118(50.07%)</t>
+          <t>268(50.28%)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>50.07%</t>
+          <t>50.28%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dermatology service</t>
+          <t>diabetes service</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2068,26 +2068,26 @@
         </is>
       </c>
       <c r="C62">
-        <v>1115</v>
+        <v>265</v>
       </c>
       <c r="D62">
-        <v>49.93</v>
+        <v>49.72</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1,115(49.93%)</t>
+          <t>265(49.72%)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>49.93%</t>
+          <t>49.72%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>diabetes service</t>
+          <t>diagnostic imaging service</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2096,26 +2096,26 @@
         </is>
       </c>
       <c r="C63">
-        <v>268</v>
+        <v>2933</v>
       </c>
       <c r="D63">
-        <v>50.28</v>
+        <v>49.66</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>268(50.28%)</t>
+          <t>2,933(49.66%)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>50.28%</t>
+          <t>49.66%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>diabetes service</t>
+          <t>diagnostic imaging service</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2124,26 +2124,26 @@
         </is>
       </c>
       <c r="C64">
-        <v>265</v>
+        <v>2973</v>
       </c>
       <c r="D64">
-        <v>49.72</v>
+        <v>50.34</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>265(49.72%)</t>
+          <t>2,973(50.34%)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>49.72%</t>
+          <t>50.34%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>diagnostic imaging service</t>
+          <t>dietetics service</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2152,26 +2152,26 @@
         </is>
       </c>
       <c r="C65">
-        <v>2933</v>
+        <v>229</v>
       </c>
       <c r="D65">
-        <v>49.66</v>
+        <v>50.33</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2,933(49.66%)</t>
+          <t>229(50.33%)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>49.66%</t>
+          <t>50.33%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>diagnostic imaging service</t>
+          <t>dietetics service</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2180,26 +2180,26 @@
         </is>
       </c>
       <c r="C66">
-        <v>2973</v>
+        <v>226</v>
       </c>
       <c r="D66">
-        <v>50.34</v>
+        <v>49.67</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2,973(50.34%)</t>
+          <t>226(49.67%)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>50.34%</t>
+          <t>49.67%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dietetics service</t>
+          <t>ear nose and throat service</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2208,26 +2208,26 @@
         </is>
       </c>
       <c r="C67">
-        <v>229</v>
+        <v>1182</v>
       </c>
       <c r="D67">
-        <v>50.33</v>
+        <v>49.68</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>229(50.33%)</t>
+          <t>1,182(49.68%)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>50.33%</t>
+          <t>49.68%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dietetics service</t>
+          <t>ear nose and throat service</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2236,26 +2236,26 @@
         </is>
       </c>
       <c r="C68">
-        <v>226</v>
+        <v>1197</v>
       </c>
       <c r="D68">
-        <v>49.67</v>
+        <v>50.32</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>226(49.67%)</t>
+          <t>1,197(50.32%)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>49.67%</t>
+          <t>50.32%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ear nose and throat service</t>
+          <t>elderly medicine service</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2264,26 +2264,26 @@
         </is>
       </c>
       <c r="C69">
-        <v>1182</v>
+        <v>1345</v>
       </c>
       <c r="D69">
-        <v>49.68</v>
+        <v>49.47</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1,182(49.68%)</t>
+          <t>1,345(49.47%)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>49.68%</t>
+          <t>49.47%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ear nose and throat service</t>
+          <t>elderly medicine service</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="C70">
-        <v>1197</v>
+        <v>1374</v>
       </c>
       <c r="D70">
-        <v>50.32</v>
+        <v>50.53</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1,197(50.32%)</t>
+          <t>1,374(50.53%)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>50.32%</t>
+          <t>50.53%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>elderly medicine service</t>
+          <t>emergency medicine service</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2320,26 +2320,26 @@
         </is>
       </c>
       <c r="C71">
-        <v>1345</v>
+        <v>268</v>
       </c>
       <c r="D71">
-        <v>49.47</v>
+        <v>50</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1,345(49.47%)</t>
+          <t>268(50%)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>49.47%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>elderly medicine service</t>
+          <t>emergency medicine service</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2348,26 +2348,26 @@
         </is>
       </c>
       <c r="C72">
-        <v>1374</v>
+        <v>268</v>
       </c>
       <c r="D72">
-        <v>50.53</v>
+        <v>50</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1,374(50.53%)</t>
+          <t>268(50%)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>50.53%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>emergency medicine service</t>
+          <t>endocrinology service</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2376,26 +2376,26 @@
         </is>
       </c>
       <c r="C73">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73">
-        <v>50</v>
+        <v>49.63</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>268(50%)</t>
+          <t>269(49.63%)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.63%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>emergency medicine service</t>
+          <t>endocrinology service</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2404,26 +2404,26 @@
         </is>
       </c>
       <c r="C74">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D74">
-        <v>50</v>
+        <v>50.37</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>268(50%)</t>
+          <t>273(50.37%)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.37%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>endocrinology service</t>
+          <t>gastroenterology service</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2432,26 +2432,26 @@
         </is>
       </c>
       <c r="C75">
-        <v>269</v>
+        <v>949</v>
       </c>
       <c r="D75">
-        <v>49.63</v>
+        <v>49.79</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>269(49.63%)</t>
+          <t>949(49.79%)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>49.63%</t>
+          <t>49.79%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>endocrinology service</t>
+          <t>gastroenterology service</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2460,26 +2460,26 @@
         </is>
       </c>
       <c r="C76">
-        <v>273</v>
+        <v>957</v>
       </c>
       <c r="D76">
-        <v>50.37</v>
+        <v>50.21</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>273(50.37%)</t>
+          <t>957(50.21%)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>50.37%</t>
+          <t>50.21%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>gastroenterology service</t>
+          <t>general internal medicine service</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2488,26 +2488,26 @@
         </is>
       </c>
       <c r="C77">
-        <v>949</v>
+        <v>1201</v>
       </c>
       <c r="D77">
-        <v>49.79</v>
+        <v>51.28</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>949(49.79%)</t>
+          <t>1,201(51.28%)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>49.79%</t>
+          <t>51.28%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gastroenterology service</t>
+          <t>general internal medicine service</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2516,26 +2516,26 @@
         </is>
       </c>
       <c r="C78">
-        <v>957</v>
+        <v>1141</v>
       </c>
       <c r="D78">
-        <v>50.21</v>
+        <v>48.72</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>957(50.21%)</t>
+          <t>1,141(48.72%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>50.21%</t>
+          <t>48.72%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>general internal medicine service</t>
+          <t>general surgery service</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2544,26 +2544,26 @@
         </is>
       </c>
       <c r="C79">
-        <v>1126</v>
+        <v>1062</v>
       </c>
       <c r="D79">
-        <v>49.67</v>
+        <v>50</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1,126(49.67%)</t>
+          <t>1,062(50%)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>49.67%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>general internal medicine service</t>
+          <t>general surgery service</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2572,26 +2572,26 @@
         </is>
       </c>
       <c r="C80">
-        <v>1141</v>
+        <v>1062</v>
       </c>
       <c r="D80">
-        <v>50.33</v>
+        <v>50</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1,141(50.33%)</t>
+          <t>1,062(50%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>50.33%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>general surgery service</t>
+          <t>genitourinary medicine service</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2600,26 +2600,26 @@
         </is>
       </c>
       <c r="C81">
-        <v>1062</v>
+        <v>6</v>
       </c>
       <c r="D81">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1,062(50%)</t>
+          <t>6(54.55%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>54.55%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>general surgery service</t>
+          <t>genitourinary medicine service</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2628,26 +2628,26 @@
         </is>
       </c>
       <c r="C82">
-        <v>1062</v>
+        <v>5</v>
       </c>
       <c r="D82">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1,062(50%)</t>
+          <t>5(45.45%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>45.45%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>genitourinary medicine service</t>
+          <t>gynaecological oncology service</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2656,26 +2656,26 @@
         </is>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="D83">
-        <v>54.55</v>
+        <v>49.57</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>6(54.55%)</t>
+          <t>115(49.57%)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>54.55%</t>
+          <t>49.57%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>genitourinary medicine service</t>
+          <t>gynaecological oncology service</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2684,26 +2684,26 @@
         </is>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="D84">
-        <v>45.45</v>
+        <v>50.43</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5(45.45%)</t>
+          <t>117(50.43%)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>45.45%</t>
+          <t>50.43%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>gynaecological oncology service</t>
+          <t>gynaecology service</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2712,26 +2712,26 @@
         </is>
       </c>
       <c r="C85">
-        <v>115</v>
+        <v>904</v>
       </c>
       <c r="D85">
-        <v>49.57</v>
+        <v>50</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>115(49.57%)</t>
+          <t>904(50%)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>49.57%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gynaecological oncology service</t>
+          <t>gynaecology service</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2740,26 +2740,26 @@
         </is>
       </c>
       <c r="C86">
-        <v>117</v>
+        <v>904</v>
       </c>
       <c r="D86">
-        <v>50.43</v>
+        <v>50</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>117(50.43%)</t>
+          <t>904(50%)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>50.43%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gynaecology service</t>
+          <t>haemophilia service</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2768,26 +2768,26 @@
         </is>
       </c>
       <c r="C87">
-        <v>904</v>
+        <v>8</v>
       </c>
       <c r="D87">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>904(50%)</t>
+          <t>8(53.33%)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53.33%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>gynaecology service</t>
+          <t>haemophilia service</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2796,47 +2796,47 @@
         </is>
       </c>
       <c r="C88">
-        <v>904</v>
+        <v>7</v>
       </c>
       <c r="D88">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>904(50%)</t>
+          <t>7(46.67%)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>46.67%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>haemophilia service</t>
+          <t>hepatobiliary and pancreatic surgery service</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D89">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>7(100%)</t>
+          <t>31(50%)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C90">
@@ -2871,28 +2871,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>hepatobiliary and pancreatic surgery service</t>
+          <t>hepatology service</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C91">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>49.65</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>31(50%)</t>
+          <t>70(49.65%)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.65%</t>
         </is>
       </c>
     </row>
@@ -2904,51 +2904,51 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C92">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D92">
-        <v>49.65</v>
+        <v>50.35</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>70(49.65%)</t>
+          <t>71(50.35%)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>49.65%</t>
+          <t>50.35%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>hepatology service</t>
+          <t>infectious diseases service</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C93">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="D93">
-        <v>50.35</v>
+        <v>50</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>71(50.35%)</t>
+          <t>26(50%)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>50.35%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C94">
@@ -2983,7 +2983,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>infectious diseases service</t>
+          <t>intensive care medicine service</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2992,47 +2992,47 @@
         </is>
       </c>
       <c r="C95">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D95">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>26(50%)</t>
+          <t>10(100%)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>intensive care medicine service</t>
+          <t>intermediate care service</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="D96">
-        <v>100</v>
+        <v>56.41</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10(100%)</t>
+          <t>176(56.41%)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56.41%</t>
         </is>
       </c>
     </row>
@@ -3044,51 +3044,51 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C97">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="D97">
-        <v>55.26</v>
+        <v>43.59</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>168(55.26%)</t>
+          <t>136(43.59%)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>55.26%</t>
+          <t>43.59%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>intermediate care service</t>
+          <t>interventional radiology service</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C98">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c r="D98">
-        <v>44.74</v>
+        <v>59.48</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>136(44.74%)</t>
+          <t>251(59.48%)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>44.74%</t>
+          <t>59.48%</t>
         </is>
       </c>
     </row>
@@ -3100,51 +3100,51 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C99">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D99">
-        <v>50.15</v>
+        <v>40.52</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>172(50.15%)</t>
+          <t>171(40.52%)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>50.15%</t>
+          <t>40.52%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>interventional radiology service</t>
+          <t>learning disability service</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C100">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="D100">
-        <v>49.85</v>
+        <v>50</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>171(49.85%)</t>
+          <t>41(50%)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>49.85%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C101">
@@ -3179,28 +3179,28 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>learning disability service</t>
+          <t>liaison psychiatry service</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C102">
-        <v>41</v>
+        <v>220</v>
       </c>
       <c r="D102">
-        <v>50</v>
+        <v>87.3</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>41(50%)</t>
+          <t>220(87.3%)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>87.3%</t>
         </is>
       </c>
     </row>
@@ -3212,58 +3212,58 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C103">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D103">
-        <v>46.67</v>
+        <v>12.7</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>28(46.67%)</t>
+          <t>32(12.7%)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>liaison psychiatry service</t>
+          <t>local specialist rehabilitation service</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C104">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D104">
-        <v>53.33</v>
+        <v>100</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>32(53.33%)</t>
+          <t>5(100%)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>53.33%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>local specialist rehabilitation service</t>
+          <t>maxillofacial surgery service</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3272,19 +3272,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>258</v>
       </c>
       <c r="D105">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2(100%)</t>
+          <t>258(50%)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C106">
@@ -3319,23 +3319,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>maxillofacial surgery service</t>
+          <t>medical oncology service</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C107">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="D107">
         <v>50</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>258(50%)</t>
+          <t>73(50%)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C108">
@@ -3375,7 +3375,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>medical oncology service</t>
+          <t>medical ophthalmology service</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3384,26 +3384,26 @@
         </is>
       </c>
       <c r="C109">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D109">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>73(50%)</t>
+          <t>58(100%)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>medical ophthalmology service</t>
+          <t>medical psychotherapy service</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="C110">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D110">
-        <v>49.57</v>
+        <v>50</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>57(49.57%)</t>
+          <t>3(50%)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>49.57%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>medical ophthalmology service</t>
+          <t>medical psychotherapy service</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3440,26 +3440,26 @@
         </is>
       </c>
       <c r="C111">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="D111">
-        <v>50.43</v>
+        <v>50</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>58(50.43%)</t>
+          <t>3(50%)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>50.43%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>medical psychotherapy service</t>
+          <t>neurology service</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3468,26 +3468,26 @@
         </is>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>762</v>
       </c>
       <c r="D112">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3(50%)</t>
+          <t>762(49.9%)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>medical psychotherapy service</t>
+          <t>neurology service</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3496,26 +3496,26 @@
         </is>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>765</v>
       </c>
       <c r="D113">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3(50%)</t>
+          <t>765(50.1%)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.1%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>neurology service</t>
+          <t>neurosurgical service</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3524,26 +3524,26 @@
         </is>
       </c>
       <c r="C114">
-        <v>762</v>
+        <v>301</v>
       </c>
       <c r="D114">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>762(49.9%)</t>
+          <t>301(50%)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>neurology service</t>
+          <t>neurosurgical service</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3552,26 +3552,26 @@
         </is>
       </c>
       <c r="C115">
-        <v>765</v>
+        <v>301</v>
       </c>
       <c r="D115">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>765(50.1%)</t>
+          <t>301(50%)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>neurosurgical service</t>
+          <t>nuclear medicine service</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3580,26 +3580,26 @@
         </is>
       </c>
       <c r="C116">
-        <v>301</v>
+        <v>30</v>
       </c>
       <c r="D116">
-        <v>50</v>
+        <v>50.85</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>301(50%)</t>
+          <t>30(50.85%)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.85%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>neurosurgical service</t>
+          <t>nuclear medicine service</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3608,26 +3608,26 @@
         </is>
       </c>
       <c r="C117">
-        <v>301</v>
+        <v>29</v>
       </c>
       <c r="D117">
-        <v>50</v>
+        <v>49.15</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>301(50%)</t>
+          <t>29(49.15%)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.15%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nuclear medicine service</t>
+          <t>obstetrics service</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3636,26 +3636,26 @@
         </is>
       </c>
       <c r="C118">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D118">
-        <v>50.85</v>
+        <v>44.44</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>30(50.85%)</t>
+          <t>4(44.44%)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>50.85%</t>
+          <t>44.44%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>nuclear medicine service</t>
+          <t>obstetrics service</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3664,26 +3664,26 @@
         </is>
       </c>
       <c r="C119">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D119">
-        <v>49.15</v>
+        <v>55.56</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>29(49.15%)</t>
+          <t>5(55.56%)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>49.15%</t>
+          <t>55.56%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>obstetrics service</t>
+          <t>occupational therapy service</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3692,26 +3692,26 @@
         </is>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>616</v>
       </c>
       <c r="D120">
-        <v>44.44</v>
+        <v>49.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>4(44.44%)</t>
+          <t>616(49.8%)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>44.44%</t>
+          <t>49.8%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>obstetrics service</t>
+          <t>occupational therapy service</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3720,26 +3720,26 @@
         </is>
       </c>
       <c r="C121">
-        <v>5</v>
+        <v>621</v>
       </c>
       <c r="D121">
-        <v>55.56</v>
+        <v>50.2</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>5(55.56%)</t>
+          <t>621(50.2%)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>55.56%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>occupational therapy service</t>
+          <t>old age psychiatry service</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3748,26 +3748,26 @@
         </is>
       </c>
       <c r="C122">
-        <v>616</v>
+        <v>464</v>
       </c>
       <c r="D122">
-        <v>49.8</v>
+        <v>49.52</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>616(49.8%)</t>
+          <t>464(49.52%)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.52%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>occupational therapy service</t>
+          <t>old age psychiatry service</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3776,26 +3776,26 @@
         </is>
       </c>
       <c r="C123">
-        <v>621</v>
+        <v>473</v>
       </c>
       <c r="D123">
-        <v>50.2</v>
+        <v>50.48</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>621(50.2%)</t>
+          <t>473(50.48%)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.48%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>old age psychiatry service</t>
+          <t>ophthalmology service</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3804,26 +3804,26 @@
         </is>
       </c>
       <c r="C124">
-        <v>464</v>
+        <v>3333</v>
       </c>
       <c r="D124">
-        <v>49.52</v>
+        <v>50.02</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>464(49.52%)</t>
+          <t>3,333(50.02%)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>49.52%</t>
+          <t>50.02%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>old age psychiatry service</t>
+          <t>ophthalmology service</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3832,26 +3832,26 @@
         </is>
       </c>
       <c r="C125">
-        <v>473</v>
+        <v>3331</v>
       </c>
       <c r="D125">
-        <v>50.48</v>
+        <v>49.98</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>473(50.48%)</t>
+          <t>3,331(49.98%)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>50.48%</t>
+          <t>49.98%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ophthalmology service</t>
+          <t>optometry service</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3860,26 +3860,26 @@
         </is>
       </c>
       <c r="C126">
-        <v>3308</v>
+        <v>37</v>
       </c>
       <c r="D126">
-        <v>49.83</v>
+        <v>48.05</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>3,308(49.83%)</t>
+          <t>37(48.05%)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>49.83%</t>
+          <t>48.05%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ophthalmology service</t>
+          <t>optometry service</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3888,26 +3888,26 @@
         </is>
       </c>
       <c r="C127">
-        <v>3331</v>
+        <v>40</v>
       </c>
       <c r="D127">
-        <v>50.17</v>
+        <v>51.95</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>3,331(50.17%)</t>
+          <t>40(51.95%)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>50.17%</t>
+          <t>51.95%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>optometry service</t>
+          <t>oral surgery service</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3916,26 +3916,26 @@
         </is>
       </c>
       <c r="C128">
-        <v>37</v>
+        <v>350</v>
       </c>
       <c r="D128">
-        <v>48.05</v>
+        <v>49.86</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>37(48.05%)</t>
+          <t>350(49.86%)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>48.05%</t>
+          <t>49.86%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>optometry service</t>
+          <t>oral surgery service</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3944,26 +3944,26 @@
         </is>
       </c>
       <c r="C129">
-        <v>40</v>
+        <v>352</v>
       </c>
       <c r="D129">
-        <v>51.95</v>
+        <v>50.14</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>40(51.95%)</t>
+          <t>352(50.14%)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>51.95%</t>
+          <t>50.14%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>oral surgery service</t>
+          <t>orthodontic service</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3972,26 +3972,26 @@
         </is>
       </c>
       <c r="C130">
-        <v>350</v>
+        <v>3</v>
       </c>
       <c r="D130">
-        <v>49.86</v>
+        <v>50</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>350(49.86%)</t>
+          <t>3(50%)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>49.86%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>oral surgery service</t>
+          <t>orthodontic service</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="C131">
-        <v>352</v>
+        <v>3</v>
       </c>
       <c r="D131">
-        <v>50.14</v>
+        <v>50</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>352(50.14%)</t>
+          <t>3(50%)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>50.14%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>orthodontic service</t>
+          <t>orthoptics service</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4028,14 +4028,14 @@
         </is>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="D132">
         <v>50</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3(50%)</t>
+          <t>178(50%)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4047,7 +4047,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>orthodontic service</t>
+          <t>orthoptics service</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4056,14 +4056,14 @@
         </is>
       </c>
       <c r="C133">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="D133">
         <v>50</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3(50%)</t>
+          <t>178(50%)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>orthoptics service</t>
+          <t>orthotics service</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4084,26 +4084,26 @@
         </is>
       </c>
       <c r="C134">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="D134">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>178(50%)</t>
+          <t>252(49.7%)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.7%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>orthoptics service</t>
+          <t>orthotics service</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4112,26 +4112,26 @@
         </is>
       </c>
       <c r="C135">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="D135">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>178(50%)</t>
+          <t>255(50.3%)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>orthotics service</t>
+          <t>paediatric ear nose and throat service</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4140,26 +4140,26 @@
         </is>
       </c>
       <c r="C136">
-        <v>252</v>
+        <v>1</v>
       </c>
       <c r="D136">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>252(49.7%)</t>
+          <t>1(50%)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>orthotics service</t>
+          <t>paediatric ear nose and throat service</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4168,26 +4168,26 @@
         </is>
       </c>
       <c r="C137">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="D137">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>255(50.3%)</t>
+          <t>1(50%)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>paediatric ear nose and throat service</t>
+          <t>paediatric ophthalmology service</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4196,14 +4196,14 @@
         </is>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D138">
         <v>50</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1(50%)</t>
+          <t>7(50%)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>paediatric ear nose and throat service</t>
+          <t>paediatric ophthalmology service</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4224,14 +4224,14 @@
         </is>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D139">
         <v>50</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1(50%)</t>
+          <t>7(50%)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4243,7 +4243,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>paediatric ophthalmology service</t>
+          <t>paediatric service</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4252,14 +4252,14 @@
         </is>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D140">
         <v>50</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>7(50%)</t>
+          <t>2(50%)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>paediatric ophthalmology service</t>
+          <t>paediatric service</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4280,14 +4280,14 @@
         </is>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D141">
         <v>50</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>7(50%)</t>
+          <t>2(50%)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4299,7 +4299,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>paediatric service</t>
+          <t>paediatric trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4308,14 +4308,14 @@
         </is>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D142">
         <v>50</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2(50%)</t>
+          <t>15(50%)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4327,7 +4327,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>paediatric service</t>
+          <t>paediatric trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4336,14 +4336,14 @@
         </is>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D143">
         <v>50</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2(50%)</t>
+          <t>15(50%)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>paediatric trauma and orthopaedic service</t>
+          <t>pain management service</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4364,26 +4364,26 @@
         </is>
       </c>
       <c r="C144">
-        <v>15</v>
+        <v>473</v>
       </c>
       <c r="D144">
-        <v>50</v>
+        <v>49.58</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>15(50%)</t>
+          <t>473(49.58%)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.58%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>paediatric trauma and orthopaedic service</t>
+          <t>pain management service</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4392,26 +4392,26 @@
         </is>
       </c>
       <c r="C145">
-        <v>15</v>
+        <v>481</v>
       </c>
       <c r="D145">
-        <v>50</v>
+        <v>50.42</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15(50%)</t>
+          <t>481(50.42%)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.42%</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>pain management service</t>
+          <t>palliative medicine service</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4420,26 +4420,26 @@
         </is>
       </c>
       <c r="C146">
-        <v>473</v>
+        <v>34</v>
       </c>
       <c r="D146">
-        <v>49.58</v>
+        <v>50.75</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>473(49.58%)</t>
+          <t>34(50.75%)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>49.58%</t>
+          <t>50.75%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>pain management service</t>
+          <t>palliative medicine service</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4448,26 +4448,26 @@
         </is>
       </c>
       <c r="C147">
-        <v>481</v>
+        <v>33</v>
       </c>
       <c r="D147">
-        <v>50.42</v>
+        <v>49.25</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>481(50.42%)</t>
+          <t>33(49.25%)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>50.42%</t>
+          <t>49.25%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>palliative medicine service</t>
+          <t>physiotherapy service</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4476,26 +4476,26 @@
         </is>
       </c>
       <c r="C148">
-        <v>34</v>
+        <v>5351</v>
       </c>
       <c r="D148">
-        <v>50.75</v>
+        <v>49.66</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>34(50.75%)</t>
+          <t>5,351(49.66%)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>50.75%</t>
+          <t>49.66%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>palliative medicine service</t>
+          <t>physiotherapy service</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4504,26 +4504,26 @@
         </is>
       </c>
       <c r="C149">
-        <v>33</v>
+        <v>5425</v>
       </c>
       <c r="D149">
-        <v>49.25</v>
+        <v>50.34</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>33(49.25%)</t>
+          <t>5,425(50.34%)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>49.25%</t>
+          <t>50.34%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>physiotherapy service</t>
+          <t>plastic surgery service</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4532,26 +4532,26 @@
         </is>
       </c>
       <c r="C150">
-        <v>5351</v>
+        <v>357</v>
       </c>
       <c r="D150">
-        <v>49.66</v>
+        <v>49.86</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>5,351(49.66%)</t>
+          <t>357(49.86%)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>49.66%</t>
+          <t>49.86%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>physiotherapy service</t>
+          <t>plastic surgery service</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4560,26 +4560,26 @@
         </is>
       </c>
       <c r="C151">
-        <v>5425</v>
+        <v>359</v>
       </c>
       <c r="D151">
-        <v>50.34</v>
+        <v>50.14</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>5,425(50.34%)</t>
+          <t>359(50.14%)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>50.34%</t>
+          <t>50.14%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>plastic surgery service</t>
+          <t>podiatric surgery service</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4588,26 +4588,26 @@
         </is>
       </c>
       <c r="C152">
-        <v>357</v>
+        <v>15</v>
       </c>
       <c r="D152">
-        <v>49.86</v>
+        <v>50</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>357(49.86%)</t>
+          <t>15(50%)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>49.86%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>plastic surgery service</t>
+          <t>podiatric surgery service</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4616,26 +4616,26 @@
         </is>
       </c>
       <c r="C153">
-        <v>359</v>
+        <v>15</v>
       </c>
       <c r="D153">
-        <v>50.14</v>
+        <v>50</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>359(50.14%)</t>
+          <t>15(50%)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>50.14%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>podiatric surgery service</t>
+          <t>podiatry service</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4644,14 +4644,14 @@
         </is>
       </c>
       <c r="C154">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="D154">
         <v>50</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>15(50%)</t>
+          <t>372(50%)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -4663,7 +4663,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>podiatric surgery service</t>
+          <t>podiatry service</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4672,14 +4672,14 @@
         </is>
       </c>
       <c r="C155">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="D155">
         <v>50</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>15(50%)</t>
+          <t>372(50%)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -4691,7 +4691,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>podiatry service</t>
+          <t>prosthetics service</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4700,14 +4700,14 @@
         </is>
       </c>
       <c r="C156">
-        <v>372</v>
+        <v>4</v>
       </c>
       <c r="D156">
         <v>50</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>372(50%)</t>
+          <t>4(50%)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>podiatry service</t>
+          <t>prosthetics service</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4728,14 +4728,14 @@
         </is>
       </c>
       <c r="C157">
-        <v>372</v>
+        <v>4</v>
       </c>
       <c r="D157">
         <v>50</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>372(50%)</t>
+          <t>4(50%)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -4747,7 +4747,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>prosthetics service</t>
+          <t>pulmonary rehabilitation service</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4756,14 +4756,14 @@
         </is>
       </c>
       <c r="C158">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D158">
         <v>50</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4(50%)</t>
+          <t>6(50%)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>prosthetics service</t>
+          <t>pulmonary rehabilitation service</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4784,14 +4784,14 @@
         </is>
       </c>
       <c r="C159">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D159">
         <v>50</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>4(50%)</t>
+          <t>6(50%)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>pulmonary rehabilitation service</t>
+          <t>rehabilitation medicine service</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4812,26 +4812,26 @@
         </is>
       </c>
       <c r="C160">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="D160">
-        <v>50</v>
+        <v>50.08</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>6(50%)</t>
+          <t>318(50.08%)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.08%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>pulmonary rehabilitation service</t>
+          <t>rehabilitation medicine service</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4840,26 +4840,26 @@
         </is>
       </c>
       <c r="C161">
-        <v>6</v>
+        <v>317</v>
       </c>
       <c r="D161">
-        <v>50</v>
+        <v>49.92</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>6(50%)</t>
+          <t>317(49.92%)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.92%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rehabilitation medicine service</t>
+          <t>renal medicine service</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4868,26 +4868,26 @@
         </is>
       </c>
       <c r="C162">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="D162">
-        <v>50.08</v>
+        <v>49.43</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>318(50.08%)</t>
+          <t>259(49.43%)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>50.08%</t>
+          <t>49.43%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rehabilitation medicine service</t>
+          <t>renal medicine service</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4896,26 +4896,26 @@
         </is>
       </c>
       <c r="C163">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="D163">
-        <v>49.92</v>
+        <v>50.57</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>317(49.92%)</t>
+          <t>265(50.57%)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>49.92%</t>
+          <t>50.57%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>renal medicine service</t>
+          <t>respiratory medicine service</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4924,26 +4924,26 @@
         </is>
       </c>
       <c r="C164">
-        <v>259</v>
+        <v>867</v>
       </c>
       <c r="D164">
-        <v>49.43</v>
+        <v>49.97</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>259(49.43%)</t>
+          <t>867(49.97%)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>49.43%</t>
+          <t>49.97%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>renal medicine service</t>
+          <t>respiratory medicine service</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4952,26 +4952,26 @@
         </is>
       </c>
       <c r="C165">
-        <v>265</v>
+        <v>868</v>
       </c>
       <c r="D165">
-        <v>50.57</v>
+        <v>50.03</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>265(50.57%)</t>
+          <t>868(50.03%)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>50.57%</t>
+          <t>50.03%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>respiratory medicine service</t>
+          <t>respiratory physiology service</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4980,26 +4980,26 @@
         </is>
       </c>
       <c r="C166">
-        <v>867</v>
+        <v>125</v>
       </c>
       <c r="D166">
-        <v>49.97</v>
+        <v>50.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>867(49.97%)</t>
+          <t>125(50.4%)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>49.97%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>respiratory medicine service</t>
+          <t>respiratory physiology service</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5008,26 +5008,26 @@
         </is>
       </c>
       <c r="C167">
-        <v>868</v>
+        <v>123</v>
       </c>
       <c r="D167">
-        <v>50.03</v>
+        <v>49.6</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>868(50.03%)</t>
+          <t>123(49.6%)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>50.03%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>respiratory physiology service</t>
+          <t>restorative dentistry service</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5036,26 +5036,26 @@
         </is>
       </c>
       <c r="C168">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="D168">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>125(50.4%)</t>
+          <t>86(50%)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>respiratory physiology service</t>
+          <t>restorative dentistry service</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5064,26 +5064,26 @@
         </is>
       </c>
       <c r="C169">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="D169">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>123(49.6%)</t>
+          <t>86(50%)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>restorative dentistry service</t>
+          <t>rheumatology service</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5092,26 +5092,26 @@
         </is>
       </c>
       <c r="C170">
-        <v>86</v>
+        <v>2194</v>
       </c>
       <c r="D170">
-        <v>50</v>
+        <v>50.01</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>86(50%)</t>
+          <t>2,194(50.01%)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.01%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>restorative dentistry service</t>
+          <t>rheumatology service</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5120,82 +5120,82 @@
         </is>
       </c>
       <c r="C171">
-        <v>86</v>
+        <v>2193</v>
       </c>
       <c r="D171">
-        <v>50</v>
+        <v>49.99</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>86(50%)</t>
+          <t>2,193(49.99%)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>49.99%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>rheumatology service</t>
+          <t>specialist rehabilitation service</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C172">
-        <v>2194</v>
+        <v>2</v>
       </c>
       <c r="D172">
-        <v>50.01</v>
+        <v>100</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2,194(50.01%)</t>
+          <t>2(100%)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>50.01%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>rheumatology service</t>
+          <t>speech and language therapy service</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C173">
-        <v>2193</v>
+        <v>87</v>
       </c>
       <c r="D173">
-        <v>49.99</v>
+        <v>49.71</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2,193(49.99%)</t>
+          <t>87(49.71%)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>49.99%</t>
+          <t>49.71%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>specialist rehabilitation service</t>
+          <t>speech and language therapy service</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5204,47 +5204,47 @@
         </is>
       </c>
       <c r="C174">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="D174">
-        <v>100</v>
+        <v>50.29</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2(100%)</t>
+          <t>88(50.29%)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50.29%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>speech and language therapy service</t>
+          <t>spinal injuries service</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C175">
-        <v>88</v>
+        <v>183</v>
       </c>
       <c r="D175">
-        <v>100</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>88(100%)</t>
+          <t>183(94.82%)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94.82%</t>
         </is>
       </c>
     </row>
@@ -5256,30 +5256,30 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C176">
         <v>10</v>
       </c>
       <c r="D176">
-        <v>50</v>
+        <v>5.18</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>10(50%)</t>
+          <t>10(5.18%)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>spinal injuries service</t>
+          <t>spinal surgery service</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5288,26 +5288,26 @@
         </is>
       </c>
       <c r="C177">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="D177">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>10(50%)</t>
+          <t>171(100%)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>spinal surgery service</t>
+          <t>sport and exercise medicine service</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5316,26 +5316,26 @@
         </is>
       </c>
       <c r="C178">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="D178">
-        <v>50.58</v>
+        <v>50</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>175(50.58%)</t>
+          <t>1(50%)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>50.58%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>spinal surgery service</t>
+          <t>sport and exercise medicine service</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5344,26 +5344,26 @@
         </is>
       </c>
       <c r="C179">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="D179">
-        <v>49.42</v>
+        <v>50</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>171(49.42%)</t>
+          <t>1(50%)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>49.42%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>sport and exercise medicine service</t>
+          <t>stroke medicine service</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5372,26 +5372,26 @@
         </is>
       </c>
       <c r="C180">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D180">
-        <v>50</v>
+        <v>48.31</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1(50%)</t>
+          <t>57(48.31%)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>48.31%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>sport and exercise medicine service</t>
+          <t>stroke medicine service</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5400,26 +5400,26 @@
         </is>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D181">
-        <v>50</v>
+        <v>51.69</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1(50%)</t>
+          <t>61(51.69%)</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51.69%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>stroke medicine service</t>
+          <t>thoracic surgery service</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5428,26 +5428,26 @@
         </is>
       </c>
       <c r="C182">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D182">
-        <v>48.31</v>
+        <v>48.84</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>57(48.31%)</t>
+          <t>21(48.84%)</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>48.31%</t>
+          <t>48.84%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>stroke medicine service</t>
+          <t>thoracic surgery service</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5456,26 +5456,26 @@
         </is>
       </c>
       <c r="C183">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D183">
-        <v>51.69</v>
+        <v>51.16</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>61(51.69%)</t>
+          <t>22(51.16%)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>51.69%</t>
+          <t>51.16%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>thoracic surgery service</t>
+          <t>transient ischaemic attack service</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5484,26 +5484,26 @@
         </is>
       </c>
       <c r="C184">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="D184">
-        <v>48.84</v>
+        <v>49.79</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>21(48.84%)</t>
+          <t>116(49.79%)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>48.84%</t>
+          <t>49.79%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>thoracic surgery service</t>
+          <t>transient ischaemic attack service</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5512,26 +5512,26 @@
         </is>
       </c>
       <c r="C185">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="D185">
-        <v>51.16</v>
+        <v>50.21</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>22(51.16%)</t>
+          <t>117(50.21%)</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>51.16%</t>
+          <t>50.21%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>transient ischaemic attack service</t>
+          <t>transplant surgery service</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5540,26 +5540,26 @@
         </is>
       </c>
       <c r="C186">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="D186">
-        <v>49.79</v>
+        <v>52.17</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>116(49.79%)</t>
+          <t>12(52.17%)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>49.79%</t>
+          <t>52.17%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>transient ischaemic attack service</t>
+          <t>transplant surgery service</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5568,26 +5568,26 @@
         </is>
       </c>
       <c r="C187">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="D187">
-        <v>50.21</v>
+        <v>47.83</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>117(50.21%)</t>
+          <t>11(47.83%)</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>50.21%</t>
+          <t>47.83%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>transplant surgery service</t>
+          <t>trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5596,26 +5596,26 @@
         </is>
       </c>
       <c r="C188">
-        <v>12</v>
+        <v>16620</v>
       </c>
       <c r="D188">
-        <v>52.17</v>
+        <v>49.74</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>12(52.17%)</t>
+          <t>16,620(49.74%)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>52.17%</t>
+          <t>49.74%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>transplant surgery service</t>
+          <t>trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5624,26 +5624,26 @@
         </is>
       </c>
       <c r="C189">
-        <v>11</v>
+        <v>16794</v>
       </c>
       <c r="D189">
-        <v>47.83</v>
+        <v>50.26</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>11(47.83%)</t>
+          <t>16,794(50.26%)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>47.83%</t>
+          <t>50.26%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>trauma and orthopaedic service</t>
+          <t>tropical medicine service</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5652,26 +5652,26 @@
         </is>
       </c>
       <c r="C190">
-        <v>16620</v>
+        <v>3</v>
       </c>
       <c r="D190">
-        <v>49.74</v>
+        <v>50</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>16,620(49.74%)</t>
+          <t>3(50%)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>49.74%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>trauma and orthopaedic service</t>
+          <t>tropical medicine service</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5680,138 +5680,138 @@
         </is>
       </c>
       <c r="C191">
-        <v>16794</v>
+        <v>3</v>
       </c>
       <c r="D191">
-        <v>50.26</v>
+        <v>50</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>16,794(50.26%)</t>
+          <t>3(50%)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>50.26%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>tropical medicine service</t>
+          <t>upper gastrointenstinal surgery service</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C192">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="D192">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>3(50%)</t>
+          <t>90(100%)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>tropical medicine service</t>
+          <t>upper gastrointestinal surgery service</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C193">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="D193">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>3(50%)</t>
+          <t>89(100%)</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>upper gastrointenstinal surgery service</t>
+          <t>urology service</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="C194">
-        <v>90</v>
+        <v>552</v>
       </c>
       <c r="D194">
-        <v>100</v>
+        <v>34.61</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>90(100%)</t>
+          <t>552(34.61%)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>34.61%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>upper gastrointestinal surgery service</t>
+          <t>urology service</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>OMOP</t>
+          <t>SOURCE</t>
         </is>
       </c>
       <c r="C195">
-        <v>89</v>
+        <v>1043</v>
       </c>
       <c r="D195">
-        <v>100</v>
+        <v>65.39</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>89(100%)</t>
+          <t>1,043(65.39%)</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>65.39%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>urology service</t>
+          <t>vascular surgery service</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5820,26 +5820,26 @@
         </is>
       </c>
       <c r="C196">
-        <v>552</v>
+        <v>344</v>
       </c>
       <c r="D196">
-        <v>34.61</v>
+        <v>49.57</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>552(34.61%)</t>
+          <t>344(49.57%)</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>34.61%</t>
+          <t>49.57%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>urology service</t>
+          <t>vascular surgery service</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5848,73 +5848,17 @@
         </is>
       </c>
       <c r="C197">
-        <v>1043</v>
+        <v>350</v>
       </c>
       <c r="D197">
-        <v>65.39</v>
+        <v>50.43</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1,043(65.39%)</t>
+          <t>350(50.43%)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
-        <is>
-          <t>65.39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>vascular surgery service</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>OMOP</t>
-        </is>
-      </c>
-      <c r="C198">
-        <v>344</v>
-      </c>
-      <c r="D198">
-        <v>49.57</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>344(49.57%)</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>49.57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>vascular surgery service</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>SOURCE</t>
-        </is>
-      </c>
-      <c r="C199">
-        <v>350</v>
-      </c>
-      <c r="D199">
-        <v>50.43</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>350(50.43%)</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
         <is>
           <t>50.43%</t>
         </is>
